--- a/artfynd/A 61010-2025 artfynd.xlsx
+++ b/artfynd/A 61010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2081,6 +2081,119 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132572395</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57869</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvavaträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>817288</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7313867</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61010-2025 artfynd.xlsx
+++ b/artfynd/A 61010-2025 artfynd.xlsx
@@ -2086,7 +2086,7 @@
         <v>132572395</v>
       </c>
       <c r="B14" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61010-2025 artfynd.xlsx
+++ b/artfynd/A 61010-2025 artfynd.xlsx
@@ -2086,7 +2086,7 @@
         <v>132572395</v>
       </c>
       <c r="B14" t="n">
-        <v>57870</v>
+        <v>57874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
